--- a/diseases/d090/2020-2025.xlsx
+++ b/diseases/d090/2020-2025.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3224,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3292,6 +3377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3440,6 +3530,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3588,6 +3683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3884,6 +3989,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4032,6 +4142,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4180,6 +4295,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4328,6 +4448,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4476,6 +4601,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4624,6 +4754,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4772,6 +4907,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4920,6 +5060,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5068,6 +5213,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5216,6 +5366,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5364,6 +5519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5512,6 +5672,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5660,6 +5825,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5808,6 +5978,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5956,6 +6131,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6104,6 +6284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6252,6 +6437,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6400,6 +6590,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6548,6 +6743,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6696,6 +6896,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6844,6 +7049,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6992,6 +7202,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7140,6 +7355,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7288,6 +7508,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7436,6 +7661,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7584,6 +7814,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7732,6 +7967,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7880,6 +8120,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8028,6 +8273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8176,6 +8426,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8324,6 +8579,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8472,6 +8732,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8620,6 +8885,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8768,6 +9038,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8916,6 +9191,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9064,6 +9344,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9212,6 +9497,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9360,6 +9650,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9508,6 +9803,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9656,6 +9956,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9804,6 +10109,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9952,6 +10262,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10100,6 +10415,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10248,6 +10568,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10396,6 +10721,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10544,6 +10874,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10692,6 +11027,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10840,6 +11180,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10988,6 +11333,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11136,6 +11486,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11284,6 +11639,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11432,6 +11792,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11580,6 +11945,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11728,6 +12098,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11876,6 +12251,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12024,6 +12404,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12172,6 +12557,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12320,6 +12710,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12468,6 +12863,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12616,6 +13016,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12764,6 +13169,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12912,6 +13322,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13060,6 +13475,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13208,6 +13628,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13356,6 +13781,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13504,6 +13934,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13652,6 +14087,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13800,6 +14240,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13948,6 +14393,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14096,6 +14546,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14244,6 +14699,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14392,6 +14852,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14540,6 +15005,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14688,6 +15158,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14836,6 +15311,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14984,6 +15464,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15132,6 +15617,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15280,6 +15770,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15428,6 +15923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15576,6 +16076,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15724,6 +16229,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15872,6 +16382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16020,6 +16535,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16168,6 +16688,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16316,6 +16841,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16464,6 +16994,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16612,6 +17147,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16760,6 +17300,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16908,6 +17453,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17056,6 +17606,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17204,6 +17759,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17352,6 +17912,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17500,6 +18065,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17648,6 +18218,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17796,6 +18371,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17944,6 +18524,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18092,6 +18677,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18240,6 +18830,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18388,6 +18983,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18536,6 +19136,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18684,6 +19289,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18832,6 +19442,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18980,6 +19595,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19128,6 +19748,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19276,6 +19901,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19424,6 +20054,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19572,6 +20207,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19720,6 +20360,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19868,6 +20513,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20016,6 +20666,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20164,6 +20819,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20312,6 +20972,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20460,6 +21125,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20608,6 +21278,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20756,6 +21431,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20904,6 +21584,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21052,6 +21737,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21200,6 +21890,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21348,6 +22043,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21496,6 +22196,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21644,6 +22349,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21792,6 +22502,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21940,6 +22655,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22088,6 +22808,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22236,6 +22961,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22384,6 +23114,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22532,6 +23267,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22680,6 +23420,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22828,6 +23573,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22976,6 +23726,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23124,6 +23879,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23272,6 +24032,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23420,6 +24185,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23568,6 +24338,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23716,6 +24491,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23864,6 +24644,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24012,6 +24797,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24160,6 +24950,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24308,6 +25103,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24456,6 +25256,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24604,6 +25409,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24752,6 +25562,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24900,6 +25715,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25048,6 +25868,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25196,6 +26021,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25344,6 +26174,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25492,6 +26327,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25640,6 +26480,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25788,6 +26633,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25936,6 +26786,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26084,6 +26939,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26232,6 +27092,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26380,6 +27245,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26528,6 +27398,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26676,6 +27551,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26824,6 +27704,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26972,6 +27857,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27120,6 +28010,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27268,6 +28163,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27416,6 +28316,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27564,6 +28469,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27712,6 +28622,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27860,6 +28775,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28008,6 +28928,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28156,6 +29081,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28304,6 +29234,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28452,6 +29387,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28600,6 +29540,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28748,6 +29693,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28896,6 +29846,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29044,6 +29999,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29192,6 +30152,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29340,6 +30305,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29488,6 +30458,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29636,6 +30611,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29784,6 +30764,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29932,6 +30917,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30080,6 +31070,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30228,6 +31223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30376,6 +31376,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30524,6 +31529,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30672,6 +31682,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30820,6 +31835,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30968,6 +31988,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31116,6 +32141,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31264,6 +32294,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31412,6 +32447,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31560,6 +32600,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31708,6 +32753,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31856,6 +32906,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32004,6 +33059,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32152,6 +33212,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32300,6 +33365,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32448,6 +33518,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32596,6 +33671,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32744,6 +33824,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32892,6 +33977,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33040,6 +34130,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33188,6 +34283,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33336,6 +34436,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33484,6 +34589,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33632,6 +34742,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33780,6 +34895,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33928,6 +35048,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34076,6 +35201,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34224,6 +35354,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34372,6 +35507,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34520,6 +35660,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34668,6 +35813,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34816,6 +35966,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34964,6 +36119,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35112,6 +36272,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35260,6 +36425,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35408,6 +36578,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35556,6 +36731,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35704,6 +36884,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35852,6 +37037,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36000,6 +37190,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36148,6 +37343,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36296,6 +37496,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36444,6 +37649,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36592,6 +37802,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36740,6 +37955,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36888,6 +38108,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37036,6 +38261,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37182,6 +38412,11 @@
       <c r="S248" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO248" t="inlineStr">

--- a/diseases/d090/2020-2025.xlsx
+++ b/diseases/d090/2020-2025.xlsx
@@ -15300,9 +15300,6 @@
       <c r="O97" t="n">
         <v>1</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -15606,9 +15603,6 @@
       <c r="O99" t="n">
         <v>1</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -15759,9 +15753,6 @@
       <c r="O100" t="n">
         <v>2</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -15912,9 +15903,6 @@
       <c r="O101" t="n">
         <v>2</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -16218,9 +16206,6 @@
       <c r="O103" t="n">
         <v>2</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -16371,9 +16356,6 @@
       <c r="O104" t="n">
         <v>5</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.001463982893031963</v>
       </c>
@@ -16524,9 +16506,6 @@
       <c r="O105" t="n">
         <v>1</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -16677,9 +16656,6 @@
       <c r="O106" t="n">
         <v>1</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -16830,9 +16806,6 @@
       <c r="O107" t="n">
         <v>2</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -16983,9 +16956,6 @@
       <c r="O108" t="n">
         <v>2</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -17136,9 +17106,6 @@
       <c r="O109" t="n">
         <v>4</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.00117118631442557</v>
       </c>
@@ -17289,9 +17256,6 @@
       <c r="O110" t="n">
         <v>1</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -17442,9 +17406,6 @@
       <c r="O111" t="n">
         <v>5</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.001463982893031963</v>
       </c>
@@ -17595,9 +17556,6 @@
       <c r="O112" t="n">
         <v>4</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.00117118631442557</v>
       </c>
@@ -17748,9 +17706,6 @@
       <c r="O113" t="n">
         <v>3</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.0008783897358191777</v>
       </c>
@@ -17901,9 +17856,6 @@
       <c r="O114" t="n">
         <v>11</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.003220762364670318</v>
       </c>
@@ -18054,9 +18006,6 @@
       <c r="O115" t="n">
         <v>12</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.003513558943276711</v>
       </c>
@@ -18207,9 +18156,6 @@
       <c r="O116" t="n">
         <v>12</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.003513558943276711</v>
       </c>
@@ -18360,9 +18306,6 @@
       <c r="O117" t="n">
         <v>23</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.006734321307947029</v>
       </c>
@@ -18513,9 +18456,6 @@
       <c r="O118" t="n">
         <v>23</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.006734321307947029</v>
       </c>
@@ -18666,9 +18606,6 @@
       <c r="O119" t="n">
         <v>29</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.008491100779585384</v>
       </c>
@@ -18819,9 +18756,6 @@
       <c r="O120" t="n">
         <v>22</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.006441524729340635</v>
       </c>
@@ -18972,9 +18906,6 @@
       <c r="O121" t="n">
         <v>58</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.01698220155917077</v>
       </c>
@@ -19125,9 +19056,6 @@
       <c r="O122" t="n">
         <v>56</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.01639660840195798</v>
       </c>
@@ -19278,9 +19206,6 @@
       <c r="O123" t="n">
         <v>60</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.01756779471638355</v>
       </c>
@@ -19431,9 +19356,6 @@
       <c r="O124" t="n">
         <v>55</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.01610381182335159</v>
       </c>
@@ -19584,9 +19506,6 @@
       <c r="O125" t="n">
         <v>26</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.007612711043766206</v>
       </c>
@@ -19737,9 +19656,6 @@
       <c r="O126" t="n">
         <v>46</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.01346864261589406</v>
       </c>
@@ -19890,9 +19806,6 @@
       <c r="O127" t="n">
         <v>33</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.009662287094010954</v>
       </c>
@@ -20043,9 +19956,6 @@
       <c r="O128" t="n">
         <v>23</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.006734321307947029</v>
       </c>
@@ -20196,9 +20106,6 @@
       <c r="O129" t="n">
         <v>25</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.007319914465159813</v>
       </c>
@@ -20349,9 +20256,6 @@
       <c r="O130" t="n">
         <v>9</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.002635169207457533</v>
       </c>
@@ -20502,9 +20406,6 @@
       <c r="O131" t="n">
         <v>13</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.003806355521883103</v>
       </c>
@@ -20655,9 +20556,6 @@
       <c r="O132" t="n">
         <v>10</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.002927965786063926</v>
       </c>
@@ -20808,9 +20706,6 @@
       <c r="O133" t="n">
         <v>14</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.004099152100489495</v>
       </c>
@@ -20961,9 +20856,6 @@
       <c r="O134" t="n">
         <v>13</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.003806355521883103</v>
       </c>
@@ -21114,9 +21006,6 @@
       <c r="O135" t="n">
         <v>8</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.00234237262885114</v>
       </c>
@@ -21267,9 +21156,6 @@
       <c r="O136" t="n">
         <v>8</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.00234237262885114</v>
       </c>
@@ -21420,9 +21306,6 @@
       <c r="O137" t="n">
         <v>4</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.00117118631442557</v>
       </c>
@@ -21573,9 +21456,6 @@
       <c r="O138" t="n">
         <v>12</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.003513558943276711</v>
       </c>
@@ -21726,9 +21606,6 @@
       <c r="O139" t="n">
         <v>7</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.002049576050244748</v>
       </c>
@@ -21879,9 +21756,6 @@
       <c r="O140" t="n">
         <v>5</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.001463982893031963</v>
       </c>
@@ -22032,9 +21906,6 @@
       <c r="O141" t="n">
         <v>3</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.0008783897358191777</v>
       </c>
@@ -22185,9 +22056,6 @@
       <c r="O142" t="n">
         <v>4</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.00117118631442557</v>
       </c>
@@ -22491,9 +22359,6 @@
       <c r="O144" t="n">
         <v>2</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -22644,9 +22509,6 @@
       <c r="O145" t="n">
         <v>1</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -22950,9 +22812,6 @@
       <c r="O147" t="n">
         <v>2</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -23103,9 +22962,6 @@
       <c r="O148" t="n">
         <v>5</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.001455700126472683</v>
       </c>
@@ -23256,9 +23112,6 @@
       <c r="O149" t="n">
         <v>3</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.0008734200758836097</v>
       </c>
@@ -23409,9 +23262,6 @@
       <c r="O150" t="n">
         <v>4</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.001164560101178146</v>
       </c>
@@ -23562,9 +23412,6 @@
       <c r="O151" t="n">
         <v>2</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -23715,9 +23562,6 @@
       <c r="O152" t="n">
         <v>3</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.0008734200758836097</v>
       </c>
@@ -23868,9 +23712,6 @@
       <c r="O153" t="n">
         <v>2</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -24021,9 +23862,6 @@
       <c r="O154" t="n">
         <v>1</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -24174,9 +24012,6 @@
       <c r="O155" t="n">
         <v>1</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -24480,9 +24315,6 @@
       <c r="O157" t="n">
         <v>3</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.0008734200758836097</v>
       </c>
@@ -24633,9 +24465,6 @@
       <c r="O158" t="n">
         <v>3</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.0008734200758836097</v>
       </c>
@@ -24786,9 +24615,6 @@
       <c r="O159" t="n">
         <v>2</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -24939,9 +24765,6 @@
       <c r="O160" t="n">
         <v>3</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.0008734200758836097</v>
       </c>
@@ -25092,9 +24915,6 @@
       <c r="O161" t="n">
         <v>3</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.0008734200758836097</v>
       </c>
@@ -25245,9 +25065,6 @@
       <c r="O162" t="n">
         <v>4</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.001164560101178146</v>
       </c>
@@ -25398,9 +25215,6 @@
       <c r="O163" t="n">
         <v>4</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.001164560101178146</v>
       </c>
@@ -25551,9 +25365,6 @@
       <c r="O164" t="n">
         <v>4</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.001164560101178146</v>
       </c>
@@ -25704,9 +25515,6 @@
       <c r="O165" t="n">
         <v>6</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.001746840151767219</v>
       </c>
@@ -25857,9 +25665,6 @@
       <c r="O166" t="n">
         <v>3</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.0008734200758836097</v>
       </c>
@@ -26010,9 +25815,6 @@
       <c r="O167" t="n">
         <v>14</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.004075960354123511</v>
       </c>
@@ -26163,9 +25965,6 @@
       <c r="O168" t="n">
         <v>15</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.004367100379418048</v>
       </c>
@@ -26316,9 +26115,6 @@
       <c r="O169" t="n">
         <v>23</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.00669622058177434</v>
       </c>
@@ -26469,9 +26265,6 @@
       <c r="O170" t="n">
         <v>44</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.01281016111295961</v>
       </c>
@@ -26622,9 +26415,6 @@
       <c r="O171" t="n">
         <v>52</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.0151392813153159</v>
       </c>
@@ -26775,9 +26565,6 @@
       <c r="O172" t="n">
         <v>82</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.02387348207415199</v>
       </c>
@@ -26928,9 +26715,6 @@
       <c r="O173" t="n">
         <v>91</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.02649374230180283</v>
       </c>
@@ -27081,9 +26865,6 @@
       <c r="O174" t="n">
         <v>113</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.03289882285828263</v>
       </c>
@@ -27234,9 +27015,6 @@
       <c r="O175" t="n">
         <v>97</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.02824058245357004</v>
       </c>
@@ -27387,9 +27165,6 @@
       <c r="O176" t="n">
         <v>93</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.0270760223523919</v>
       </c>
@@ -27540,9 +27315,6 @@
       <c r="O177" t="n">
         <v>88</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0.02562032222591921</v>
       </c>
@@ -27693,9 +27465,6 @@
       <c r="O178" t="n">
         <v>78</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.02270892197297385</v>
       </c>
@@ -27846,9 +27615,6 @@
       <c r="O179" t="n">
         <v>61</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0.01775954154296673</v>
       </c>
@@ -27999,9 +27765,6 @@
       <c r="O180" t="n">
         <v>29</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.00844306073354156</v>
       </c>
@@ -28152,9 +27915,6 @@
       <c r="O181" t="n">
         <v>46</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0.01339244116354868</v>
       </c>
@@ -28305,9 +28065,6 @@
       <c r="O182" t="n">
         <v>47</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.01368358118884322</v>
       </c>
@@ -28458,9 +28215,6 @@
       <c r="O183" t="n">
         <v>24</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.006987360607068878</v>
       </c>
@@ -28611,9 +28365,6 @@
       <c r="O184" t="n">
         <v>38</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.01106332096119239</v>
       </c>
@@ -28764,9 +28515,6 @@
       <c r="O185" t="n">
         <v>17</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.004949380430007121</v>
       </c>
@@ -28917,9 +28665,6 @@
       <c r="O186" t="n">
         <v>18</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.005240520455301658</v>
       </c>
@@ -29070,9 +28815,6 @@
       <c r="O187" t="n">
         <v>30</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.008734200758836096</v>
       </c>
@@ -29223,9 +28965,6 @@
       <c r="O188" t="n">
         <v>25</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.007278500632363413</v>
       </c>
@@ -29376,9 +29115,6 @@
       <c r="O189" t="n">
         <v>25</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.007278500632363413</v>
       </c>
@@ -29529,9 +29265,6 @@
       <c r="O190" t="n">
         <v>54</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.01572156136590497</v>
       </c>
@@ -29682,9 +29415,6 @@
       <c r="O191" t="n">
         <v>22</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0.006405080556479804</v>
       </c>
@@ -29835,9 +29565,6 @@
       <c r="O192" t="n">
         <v>19</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.005531660480596195</v>
       </c>
@@ -29988,9 +29715,6 @@
       <c r="O193" t="n">
         <v>18</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.005240520455301658</v>
       </c>
@@ -30141,9 +29865,6 @@
       <c r="O194" t="n">
         <v>13</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.003784820328828975</v>
       </c>
@@ -30294,9 +30015,6 @@
       <c r="O195" t="n">
         <v>10</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0.002911400252945365</v>
       </c>
@@ -30447,9 +30165,6 @@
       <c r="O196" t="n">
         <v>6</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.001746840151767219</v>
       </c>
@@ -30600,9 +30315,6 @@
       <c r="O197" t="n">
         <v>1</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -30753,9 +30465,6 @@
       <c r="O198" t="n">
         <v>1</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -30906,9 +30615,6 @@
       <c r="O199" t="n">
         <v>3</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -31059,9 +30765,6 @@
       <c r="O200" t="n">
         <v>2</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -31212,9 +30915,6 @@
       <c r="O201" t="n">
         <v>3</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -31365,9 +31065,6 @@
       <c r="O202" t="n">
         <v>1</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -31518,9 +31215,6 @@
       <c r="O203" t="n">
         <v>2</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -31671,9 +31365,6 @@
       <c r="O204" t="n">
         <v>2</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -31824,9 +31515,6 @@
       <c r="O205" t="n">
         <v>3</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -31977,9 +31665,6 @@
       <c r="O206" t="n">
         <v>2</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -32130,9 +31815,6 @@
       <c r="O207" t="n">
         <v>1</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -32283,9 +31965,6 @@
       <c r="O208" t="n">
         <v>6</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.00173698276384187</v>
       </c>
@@ -32436,9 +32115,6 @@
       <c r="O209" t="n">
         <v>1</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -32589,9 +32265,6 @@
       <c r="O210" t="n">
         <v>1</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -32742,9 +32415,6 @@
       <c r="O211" t="n">
         <v>2</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -32895,9 +32565,6 @@
       <c r="O212" t="n">
         <v>5</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0.001447485636534892</v>
       </c>
@@ -33048,9 +32715,6 @@
       <c r="O213" t="n">
         <v>2</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -33201,9 +32865,6 @@
       <c r="O214" t="n">
         <v>4</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.001157988509227914</v>
       </c>
@@ -33507,9 +33168,6 @@
       <c r="O216" t="n">
         <v>2</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -33660,9 +33318,6 @@
       <c r="O217" t="n">
         <v>9</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0.002605474145762805</v>
       </c>
@@ -33813,9 +33468,6 @@
       <c r="O218" t="n">
         <v>2</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -33966,9 +33618,6 @@
       <c r="O219" t="n">
         <v>17</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0.004921451164218632</v>
       </c>
@@ -34119,9 +33768,6 @@
       <c r="O220" t="n">
         <v>17</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.004921451164218632</v>
       </c>
@@ -34272,9 +33918,6 @@
       <c r="O221" t="n">
         <v>50</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0.01447485636534892</v>
       </c>
@@ -34425,9 +34068,6 @@
       <c r="O222" t="n">
         <v>55</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.01592234200188381</v>
       </c>
@@ -34578,9 +34218,6 @@
       <c r="O223" t="n">
         <v>46</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.01331686785612101</v>
       </c>
@@ -34731,9 +34368,6 @@
       <c r="O224" t="n">
         <v>99</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.02866021560339085</v>
       </c>
@@ -34884,9 +34518,6 @@
       <c r="O225" t="n">
         <v>63</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.01823831902033964</v>
       </c>
@@ -35037,9 +34668,6 @@
       <c r="O226" t="n">
         <v>63</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0.01823831902033964</v>
       </c>
@@ -35190,9 +34818,6 @@
       <c r="O227" t="n">
         <v>56</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0.01621183912919079</v>
       </c>
@@ -35343,9 +34968,6 @@
       <c r="O228" t="n">
         <v>54</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.01563284487457683</v>
       </c>
@@ -35496,9 +35118,6 @@
       <c r="O229" t="n">
         <v>56</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0.01621183912919079</v>
       </c>
@@ -35649,9 +35268,6 @@
       <c r="O230" t="n">
         <v>44</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.01273787360150705</v>
       </c>
@@ -35802,9 +35418,6 @@
       <c r="O231" t="n">
         <v>56</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0.01621183912919079</v>
       </c>
@@ -35955,9 +35568,6 @@
       <c r="O232" t="n">
         <v>41</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0.01186938221958611</v>
       </c>
@@ -36108,9 +35718,6 @@
       <c r="O233" t="n">
         <v>25</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0.007237428182674459</v>
       </c>
@@ -36261,9 +35868,6 @@
       <c r="O234" t="n">
         <v>37</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0.0107113937103582</v>
       </c>
@@ -36414,9 +36018,6 @@
       <c r="O235" t="n">
         <v>20</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0.005789942546139568</v>
       </c>
@@ -36567,9 +36168,6 @@
       <c r="O236" t="n">
         <v>27</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.007816422437288416</v>
       </c>
@@ -36720,9 +36318,6 @@
       <c r="O237" t="n">
         <v>29</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0.008395416691902373</v>
       </c>
@@ -36873,9 +36468,6 @@
       <c r="O238" t="n">
         <v>21</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.006079439673446546</v>
       </c>
@@ -37026,9 +36618,6 @@
       <c r="O239" t="n">
         <v>37</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0.0107113937103582</v>
       </c>
@@ -37179,9 +36768,6 @@
       <c r="O240" t="n">
         <v>17</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0.004921451164218632</v>
       </c>
@@ -37332,9 +36918,6 @@
       <c r="O241" t="n">
         <v>14</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0.004052959782297697</v>
       </c>
@@ -37485,9 +37068,6 @@
       <c r="O242" t="n">
         <v>10</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0.002894971273069784</v>
       </c>
@@ -37638,9 +37218,6 @@
       <c r="O243" t="n">
         <v>15</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0.004342456909604675</v>
       </c>
@@ -37791,9 +37368,6 @@
       <c r="O244" t="n">
         <v>14</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0.004052959782297697</v>
       </c>
@@ -37944,9 +37518,6 @@
       <c r="O245" t="n">
         <v>16</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0.004631954036911654</v>
       </c>
@@ -38097,9 +37668,6 @@
       <c r="O246" t="n">
         <v>6</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0.00173698276384187</v>
       </c>
@@ -38250,9 +37818,6 @@
       <c r="O247" t="n">
         <v>7</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0.002026479891148849</v>
       </c>
@@ -38402,9 +37967,6 @@
       </c>
       <c r="O248" t="n">
         <v>6</v>
-      </c>
-      <c r="Q248" t="n">
-        <v>0</v>
       </c>
       <c r="R248" t="n">
         <v>0.00173698276384187</v>
